--- a/paper/RQ1/outputs/260316_collaboration_metrics.xlsx
+++ b/paper/RQ1/outputs/260316_collaboration_metrics.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20,35 +20,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>BIPs</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cluster Size</t>
+          <t>Degree</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Degree</t>
+          <t>Weighted Degree</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>Weighted Degree</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Normalized Degree</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Eigenvector Centrality</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Weighted Eigenvector</t>
         </is>
@@ -61,24 +46,15 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>31</v>
-      </c>
-      <c r="F2">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="G2">
-        <v>0.5590655690920634</v>
-      </c>
-      <c r="H2">
         <v>0.6723479476202487</v>
       </c>
     </row>
@@ -89,24 +65,15 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>7</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>0.06481481481481481</v>
-      </c>
-      <c r="G3">
-        <v>3.552916821752586e-16</v>
-      </c>
-      <c r="H3">
         <v>5.9974833125375774e-40</v>
       </c>
     </row>
@@ -117,24 +84,15 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>14</v>
-      </c>
-      <c r="F4">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="G4">
-        <v>0.28742327576783117</v>
-      </c>
-      <c r="H4">
         <v>0.5469422015705898</v>
       </c>
     </row>
@@ -145,24 +103,15 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="G5">
-        <v>0.05374622752455962</v>
-      </c>
-      <c r="H5">
         <v>0.026622433448152752</v>
       </c>
     </row>
@@ -173,24 +122,15 @@
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G6">
-        <v>0.00030785310079833476</v>
-      </c>
-      <c r="H6">
         <v>5.4151952581585055e-36</v>
       </c>
     </row>
@@ -201,24 +141,15 @@
         </is>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G7">
-        <v>0.2687906790701238</v>
-      </c>
-      <c r="H7">
         <v>0.12377562181948341</v>
       </c>
     </row>
@@ -229,24 +160,15 @@
         </is>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G8">
-        <v>0.2764654366014668</v>
-      </c>
-      <c r="H8">
         <v>0.12429230247203926</v>
       </c>
     </row>
@@ -257,24 +179,15 @@
         </is>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
       <c r="E9">
-        <v>5</v>
-      </c>
-      <c r="F9">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G9">
-        <v>0.00030785310079833476</v>
-      </c>
-      <c r="H9">
         <v>5.4151952581585055e-36</v>
       </c>
     </row>
@@ -285,24 +198,15 @@
         </is>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E10">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G10">
-        <v>0.05200585932811425</v>
-      </c>
-      <c r="H10">
         <v>0.02648861694952283</v>
       </c>
     </row>
@@ -313,24 +217,15 @@
         </is>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G11">
-        <v>0.15513564546505978</v>
-      </c>
-      <c r="H11">
         <v>0.13318631648293341</v>
       </c>
     </row>
@@ -341,24 +236,15 @@
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>5</v>
-      </c>
-      <c r="F12">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G12">
-        <v>0.00030785310079833476</v>
-      </c>
-      <c r="H12">
         <v>5.4151952581585055e-36</v>
       </c>
     </row>
@@ -369,24 +255,15 @@
         </is>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13">
-        <v>5</v>
-      </c>
-      <c r="F13">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G13">
-        <v>0.19915723658092568</v>
-      </c>
-      <c r="H13">
         <v>0.07790462267430612</v>
       </c>
     </row>
@@ -397,24 +274,15 @@
         </is>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>5</v>
-      </c>
-      <c r="F14">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G14">
-        <v>0.09900096631430726</v>
-      </c>
-      <c r="H14">
         <v>0.017054781310289608</v>
       </c>
     </row>
@@ -425,24 +293,15 @@
         </is>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>5</v>
-      </c>
-      <c r="F15">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G15">
-        <v>0.19542857314175463</v>
-      </c>
-      <c r="H15">
         <v>0.07491539025525926</v>
       </c>
     </row>
@@ -453,24 +312,15 @@
         </is>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G16">
-        <v>0.00030785310079833476</v>
-      </c>
-      <c r="H16">
         <v>5.4151952581585055e-36</v>
       </c>
     </row>
@@ -481,24 +331,15 @@
         </is>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>5</v>
-      </c>
-      <c r="F17">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G17">
-        <v>0.00030785310079833476</v>
-      </c>
-      <c r="H17">
         <v>5.4151952581585055e-36</v>
       </c>
     </row>
@@ -509,24 +350,15 @@
         </is>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>5</v>
-      </c>
-      <c r="F18">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G18">
-        <v>0.00030785310079833476</v>
-      </c>
-      <c r="H18">
         <v>5.4151952581585055e-36</v>
       </c>
     </row>
@@ -537,24 +369,15 @@
         </is>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>7</v>
-      </c>
-      <c r="F19">
-        <v>0.046296296296296294</v>
-      </c>
-      <c r="G19">
-        <v>0.22703904864894559</v>
-      </c>
-      <c r="H19">
         <v>0.16616038700654656</v>
       </c>
     </row>
@@ -565,24 +388,15 @@
         </is>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20">
-        <v>4</v>
-      </c>
-      <c r="F20">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G20">
-        <v>8.080026042607643e-14</v>
-      </c>
-      <c r="H20">
         <v>6.574957108345493e-45</v>
       </c>
     </row>
@@ -593,24 +407,15 @@
         </is>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G21">
-        <v>0.08421294211260143</v>
-      </c>
-      <c r="H21">
         <v>0.05194128232641132</v>
       </c>
     </row>
@@ -621,24 +426,15 @@
         </is>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>6</v>
-      </c>
-      <c r="F22">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G22">
-        <v>0.1510576449024129</v>
-      </c>
-      <c r="H22">
         <v>0.1525899191730247</v>
       </c>
     </row>
@@ -649,24 +445,15 @@
         </is>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G23">
-        <v>8.080026042607643e-14</v>
-      </c>
-      <c r="H23">
         <v>6.574957108345493e-45</v>
       </c>
     </row>
@@ -677,24 +464,15 @@
         </is>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>8</v>
-      </c>
-      <c r="F24">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G24">
-        <v>0.19030142374321626</v>
-      </c>
-      <c r="H24">
         <v>0.22522073761056016</v>
       </c>
     </row>
@@ -705,24 +483,15 @@
         </is>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G25">
-        <v>8.080026042607643e-14</v>
-      </c>
-      <c r="H25">
         <v>6.574957108345493e-45</v>
       </c>
     </row>
@@ -733,24 +502,15 @@
         </is>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G26">
-        <v>8.080026042607643e-14</v>
-      </c>
-      <c r="H26">
         <v>6.574957108345493e-45</v>
       </c>
     </row>
@@ -761,24 +521,15 @@
         </is>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G27">
-        <v>8.080026042607643e-14</v>
-      </c>
-      <c r="H27">
         <v>6.574957108345493e-45</v>
       </c>
     </row>
@@ -792,21 +543,12 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G28">
-        <v>0.2608393948454047</v>
-      </c>
-      <c r="H28">
         <v>0.12297351391988402</v>
       </c>
     </row>
@@ -820,21 +562,12 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G29">
-        <v>2.2084906419531247e-16</v>
-      </c>
-      <c r="H29">
         <v>4.6509005269347845e-40</v>
       </c>
     </row>
@@ -845,24 +578,15 @@
         </is>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>4</v>
-      </c>
-      <c r="F30">
-        <v>0.037037037037037035</v>
-      </c>
-      <c r="G30">
-        <v>0.08421294211260143</v>
-      </c>
-      <c r="H30">
         <v>0.05194128232641132</v>
       </c>
     </row>
@@ -873,24 +597,15 @@
         </is>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>4</v>
-      </c>
-      <c r="F31">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G31">
-        <v>1.917089441368393e-45</v>
-      </c>
-      <c r="H31">
         <v>1.6723656533443597e-64</v>
       </c>
     </row>
@@ -904,21 +619,12 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <v>3</v>
       </c>
       <c r="E32">
-        <v>3</v>
-      </c>
-      <c r="F32">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G32">
-        <v>0.18465675330877607</v>
-      </c>
-      <c r="H32">
         <v>0.07680256486050585</v>
       </c>
     </row>
@@ -929,24 +635,15 @@
         </is>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>3</v>
       </c>
       <c r="E33">
-        <v>3</v>
-      </c>
-      <c r="F33">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G33">
-        <v>1.0856582239919718e-37</v>
-      </c>
-      <c r="H33">
         <v>2.8728180194212856e-69</v>
       </c>
     </row>
@@ -957,24 +654,15 @@
         </is>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>4</v>
-      </c>
-      <c r="F34">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G34">
-        <v>0.1740214226952532</v>
-      </c>
-      <c r="H34">
         <v>0.12510306900516208</v>
       </c>
     </row>
@@ -985,24 +673,15 @@
         </is>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35">
-        <v>3</v>
-      </c>
-      <c r="F35">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G35">
-        <v>2.0153671580191682e-16</v>
-      </c>
-      <c r="H35">
         <v>2.37892157689121e-40</v>
       </c>
     </row>
@@ -1013,24 +692,15 @@
         </is>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36">
-        <v>3</v>
-      </c>
-      <c r="F36">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G36">
-        <v>2.0153671580191682e-16</v>
-      </c>
-      <c r="H36">
         <v>2.37892157689121e-40</v>
       </c>
     </row>
@@ -1041,24 +711,15 @@
         </is>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>5</v>
-      </c>
-      <c r="F37">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G37">
-        <v>2.0852656632636318e-16</v>
-      </c>
-      <c r="H37">
         <v>7.000480280659237e-40</v>
       </c>
     </row>
@@ -1069,24 +730,15 @@
         </is>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G38">
-        <v>2.0153671580191682e-16</v>
-      </c>
-      <c r="H38">
         <v>2.37892157689121e-40</v>
       </c>
     </row>
@@ -1097,24 +749,15 @@
         </is>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
       <c r="E39">
-        <v>3</v>
-      </c>
-      <c r="F39">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G39">
-        <v>0.02439134723115079</v>
-      </c>
-      <c r="H39">
         <v>0.004858214345797944</v>
       </c>
     </row>
@@ -1125,24 +768,15 @@
         </is>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>5</v>
-      </c>
-      <c r="F40">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G40">
-        <v>2.0852656632636318e-16</v>
-      </c>
-      <c r="H40">
         <v>7.000480280659237e-40</v>
       </c>
     </row>
@@ -1153,24 +787,15 @@
         </is>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>4</v>
-      </c>
-      <c r="F41">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G41">
-        <v>0.03884683836616548</v>
-      </c>
-      <c r="H41">
         <v>0.010459360527248461</v>
       </c>
     </row>
@@ -1184,21 +809,12 @@
         <v>1</v>
       </c>
       <c r="C42">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42">
-        <v>3</v>
-      </c>
-      <c r="F42">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G42">
-        <v>0.1740214226952532</v>
-      </c>
-      <c r="H42">
         <v>0.07311112214259978</v>
       </c>
     </row>
@@ -1209,24 +825,15 @@
         </is>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>4</v>
-      </c>
-      <c r="F43">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G43">
-        <v>0.03884683836616548</v>
-      </c>
-      <c r="H43">
         <v>0.010459360527248461</v>
       </c>
     </row>
@@ -1237,24 +844,15 @@
         </is>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
       <c r="E44">
-        <v>3</v>
-      </c>
-      <c r="F44">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G44">
-        <v>0.011026345371433259</v>
-      </c>
-      <c r="H44">
         <v>0.002265883487539029</v>
       </c>
     </row>
@@ -1268,21 +866,12 @@
         <v>1</v>
       </c>
       <c r="C45">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45">
-        <v>3</v>
-      </c>
-      <c r="F45">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="G45">
-        <v>0.02439134723115079</v>
-      </c>
-      <c r="H45">
         <v>0.004858214345797944</v>
       </c>
     </row>
@@ -1293,24 +882,15 @@
         </is>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>3</v>
-      </c>
-      <c r="F46">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G46">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H46">
         <v>4.1466524194273977e-60</v>
       </c>
     </row>
@@ -1321,24 +901,15 @@
         </is>
       </c>
       <c r="B47">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G47">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H47">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -1352,21 +923,12 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48">
-        <v>2</v>
-      </c>
-      <c r="F48">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G48">
-        <v>0.04593491680035786</v>
-      </c>
-      <c r="H48">
         <v>0.007125903962116736</v>
       </c>
     </row>
@@ -1380,21 +942,12 @@
         <v>1</v>
       </c>
       <c r="C49">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>2</v>
       </c>
       <c r="E49">
-        <v>2</v>
-      </c>
-      <c r="F49">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G49">
-        <v>0.07821751782862241</v>
-      </c>
-      <c r="H49">
         <v>0.03279922489054862</v>
       </c>
     </row>
@@ -1405,24 +958,15 @@
         </is>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50">
-        <v>2</v>
-      </c>
-      <c r="F50">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G50">
-        <v>9.278444255197646e-38</v>
-      </c>
-      <c r="H50">
         <v>2.455218526371594e-69</v>
       </c>
     </row>
@@ -1433,24 +977,15 @@
         </is>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>2</v>
       </c>
       <c r="E51">
-        <v>2</v>
-      </c>
-      <c r="F51">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G51">
-        <v>9.278444255197646e-38</v>
-      </c>
-      <c r="H51">
         <v>2.455218526371594e-69</v>
       </c>
     </row>
@@ -1464,21 +999,12 @@
         <v>1</v>
       </c>
       <c r="C52">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>2</v>
       </c>
       <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G52">
-        <v>0.002543187814533621</v>
-      </c>
-      <c r="H52">
         <v>0.000207261746455041</v>
       </c>
     </row>
@@ -1489,24 +1015,15 @@
         </is>
       </c>
       <c r="B53">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G53">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H53">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -1517,24 +1034,15 @@
         </is>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54">
-        <v>2</v>
-      </c>
-      <c r="F54">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G54">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H54">
         <v>3.0355602523492655e-60</v>
       </c>
     </row>
@@ -1545,24 +1053,15 @@
         </is>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G55">
-        <v>0.1338548497648529</v>
-      </c>
-      <c r="H55">
         <v>0.18020826949029017</v>
       </c>
     </row>
@@ -1573,24 +1072,15 @@
         </is>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E56">
-        <v>6</v>
-      </c>
-      <c r="F56">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G56">
-        <v>0.019819946269290727</v>
-      </c>
-      <c r="H56">
         <v>0.013353216110772666</v>
       </c>
     </row>
@@ -1601,24 +1091,15 @@
         </is>
       </c>
       <c r="B57">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
       <c r="E57">
-        <v>2</v>
-      </c>
-      <c r="F57">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G57">
-        <v>5.365940484367456e-52</v>
-      </c>
-      <c r="H57">
         <v>1.886920150820061e-86</v>
       </c>
     </row>
@@ -1629,24 +1110,15 @@
         </is>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>2</v>
       </c>
       <c r="E58">
-        <v>2</v>
-      </c>
-      <c r="F58">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G58">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H58">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -1657,24 +1129,15 @@
         </is>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59">
-        <v>2</v>
-      </c>
-      <c r="F59">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G59">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H59">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -1685,24 +1148,15 @@
         </is>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C60">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <v>2</v>
       </c>
       <c r="E60">
-        <v>2</v>
-      </c>
-      <c r="F60">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G60">
-        <v>0.019230133378873707</v>
-      </c>
-      <c r="H60">
         <v>0.0014394185922724184</v>
       </c>
     </row>
@@ -1713,24 +1167,15 @@
         </is>
       </c>
       <c r="B61">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>3</v>
-      </c>
-      <c r="F61">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G61">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H61">
         <v>4.1466524194273977e-60</v>
       </c>
     </row>
@@ -1744,21 +1189,12 @@
         <v>1</v>
       </c>
       <c r="C62">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
-      </c>
-      <c r="F62">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G62">
-        <v>0.002543187814533621</v>
-      </c>
-      <c r="H62">
         <v>0.000207261746455041</v>
       </c>
     </row>
@@ -1769,24 +1205,15 @@
         </is>
       </c>
       <c r="B63">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="F63">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G63">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H63">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -1797,24 +1224,15 @@
         </is>
       </c>
       <c r="B64">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="F64">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G64">
-        <v>1.158014658789016e-40</v>
-      </c>
-      <c r="H64">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -1828,21 +1246,12 @@
         <v>1</v>
       </c>
       <c r="C65">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>2</v>
       </c>
       <c r="E65">
-        <v>2</v>
-      </c>
-      <c r="F65">
-        <v>0.018518518518518517</v>
-      </c>
-      <c r="G65">
-        <v>0.04593491680035786</v>
-      </c>
-      <c r="H65">
         <v>0.007125903962116736</v>
       </c>
     </row>
@@ -1853,24 +1262,15 @@
         </is>
       </c>
       <c r="B66">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G66">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H66">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -1881,24 +1281,15 @@
         </is>
       </c>
       <c r="B67">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G67">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H67">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -1909,24 +1300,15 @@
         </is>
       </c>
       <c r="B68">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G68">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H68">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -1937,24 +1319,15 @@
         </is>
       </c>
       <c r="B69">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G69">
-        <v>5.002833899398688e-38</v>
-      </c>
-      <c r="H69">
         <v>1.323826509738712e-69</v>
       </c>
     </row>
@@ -1968,21 +1341,12 @@
         <v>1</v>
       </c>
       <c r="C70">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
       <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G70">
-        <v>0.01855465827063076</v>
-      </c>
-      <c r="H70">
         <v>0.0014293089287752765</v>
       </c>
     </row>
@@ -1993,24 +1357,15 @@
         </is>
       </c>
       <c r="B71">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G71">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H71">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2021,24 +1376,15 @@
         </is>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G72">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H72">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2049,24 +1395,15 @@
         </is>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
       <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G73">
-        <v>0.02831106689839962</v>
-      </c>
-      <c r="H73">
         <v>0.01278760544195237</v>
       </c>
     </row>
@@ -2077,24 +1414,15 @@
         </is>
       </c>
       <c r="B74">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G74">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H74">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2105,24 +1433,15 @@
         </is>
       </c>
       <c r="B75">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>2</v>
-      </c>
-      <c r="F75">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G75">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H75">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -2133,24 +1452,15 @@
         </is>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G76">
-        <v>5.869098443103658e-17</v>
-      </c>
-      <c r="H76">
         <v>1.0287114621900934e-40</v>
       </c>
     </row>
@@ -2161,24 +1471,15 @@
         </is>
       </c>
       <c r="B77">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
       <c r="E77">
-        <v>1</v>
-      </c>
-      <c r="F77">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G77">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H77">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2192,21 +1493,12 @@
         <v>1</v>
       </c>
       <c r="C78">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="F78">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G78">
-        <v>0.03662702017927874</v>
-      </c>
-      <c r="H78">
         <v>0.00627818908806134</v>
       </c>
     </row>
@@ -2217,24 +1509,15 @@
         </is>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>1</v>
-      </c>
-      <c r="F79">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G79">
-        <v>3.7942929039396556e-52</v>
-      </c>
-      <c r="H79">
         <v>1.886920150820061e-86</v>
       </c>
     </row>
@@ -2245,24 +1528,15 @@
         </is>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>1</v>
-      </c>
-      <c r="F80">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G80">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H80">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2273,24 +1547,15 @@
         </is>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C81">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>1</v>
-      </c>
-      <c r="F81">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G81">
-        <v>0.003604091622811635</v>
-      </c>
-      <c r="H81">
         <v>0.00012063004011717024</v>
       </c>
     </row>
@@ -2304,21 +1569,12 @@
         <v>1</v>
       </c>
       <c r="C82">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>1</v>
-      </c>
-      <c r="F82">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G82">
-        <v>0.1047794882369733</v>
-      </c>
-      <c r="H82">
         <v>0.05634894785677043</v>
       </c>
     </row>
@@ -2329,24 +1585,15 @@
         </is>
       </c>
       <c r="B83">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>1</v>
-      </c>
-      <c r="F83">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G83">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H83">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2357,24 +1604,15 @@
         </is>
       </c>
       <c r="B84">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>1</v>
-      </c>
-      <c r="F84">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G84">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H84">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2385,24 +1623,15 @@
         </is>
       </c>
       <c r="B85">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>1</v>
-      </c>
-      <c r="F85">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G85">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H85">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2413,24 +1642,15 @@
         </is>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>2</v>
-      </c>
-      <c r="F86">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G86">
-        <v>1.106832105034631e-45</v>
-      </c>
-      <c r="H86">
         <v>2.2298208711258123e-64</v>
       </c>
     </row>
@@ -2441,24 +1661,15 @@
         </is>
       </c>
       <c r="B87">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>1</v>
-      </c>
-      <c r="F87">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G87">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H87">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2469,24 +1680,15 @@
         </is>
       </c>
       <c r="B88">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
-        <v>2</v>
-      </c>
-      <c r="F88">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G88">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H88">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -2497,24 +1699,15 @@
         </is>
       </c>
       <c r="B89">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>1</v>
-      </c>
-      <c r="F89">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G89">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H89">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2525,24 +1718,15 @@
         </is>
       </c>
       <c r="B90">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90">
-        <v>2</v>
-      </c>
-      <c r="F90">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G90">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H90">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -2553,24 +1737,15 @@
         </is>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C91">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91">
-        <v>1</v>
-      </c>
-      <c r="F91">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G91">
-        <v>0.02831106689839962</v>
-      </c>
-      <c r="H91">
         <v>0.01278760544195237</v>
       </c>
     </row>
@@ -2584,21 +1759,12 @@
         <v>1</v>
       </c>
       <c r="C92">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>1</v>
-      </c>
-      <c r="F92">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G92">
-        <v>0.05037646986841767</v>
-      </c>
-      <c r="H92">
         <v>0.010373097291625558</v>
       </c>
     </row>
@@ -2609,24 +1775,15 @@
         </is>
       </c>
       <c r="B93">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>1</v>
-      </c>
-      <c r="F93">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G93">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H93">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2637,24 +1794,15 @@
         </is>
       </c>
       <c r="B94">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>1</v>
-      </c>
-      <c r="F94">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G94">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H94">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2665,24 +1813,15 @@
         </is>
       </c>
       <c r="B95">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>1</v>
-      </c>
-      <c r="F95">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G95">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H95">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2693,24 +1832,15 @@
         </is>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>1</v>
-      </c>
-      <c r="F96">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G96">
-        <v>9.441932055724548e-17</v>
-      </c>
-      <c r="H96">
         <v>1.3265559631238551e-40</v>
       </c>
     </row>
@@ -2721,24 +1851,15 @@
         </is>
       </c>
       <c r="B97">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>1</v>
-      </c>
-      <c r="F97">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G97">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H97">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2752,21 +1873,12 @@
         <v>1</v>
       </c>
       <c r="C98">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>1</v>
-      </c>
-      <c r="F98">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G98">
-        <v>0.01855465827063076</v>
-      </c>
-      <c r="H98">
         <v>0.0014293089287752765</v>
       </c>
     </row>
@@ -2777,24 +1889,15 @@
         </is>
       </c>
       <c r="B99">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G99">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H99">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2805,24 +1908,15 @@
         </is>
       </c>
       <c r="B100">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>1</v>
-      </c>
-      <c r="F100">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G100">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H100">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2833,24 +1927,15 @@
         </is>
       </c>
       <c r="B101">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>2</v>
-      </c>
-      <c r="F101">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G101">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H101">
         <v>1.3278020137673604e-72</v>
       </c>
     </row>
@@ -2861,24 +1946,15 @@
         </is>
       </c>
       <c r="B102">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>1</v>
-      </c>
-      <c r="F102">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G102">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H102">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2889,24 +1965,15 @@
         </is>
       </c>
       <c r="B103">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G103">
-        <v>3.7942929039396556e-52</v>
-      </c>
-      <c r="H103">
         <v>1.886920150820061e-86</v>
       </c>
     </row>
@@ -2917,24 +1984,15 @@
         </is>
       </c>
       <c r="B104">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="F104">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G104">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H104">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -2945,24 +2003,15 @@
         </is>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>1</v>
-      </c>
-      <c r="F105">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G105">
-        <v>1.106832105034631e-45</v>
-      </c>
-      <c r="H105">
         <v>1.1149104355629062e-64</v>
       </c>
     </row>
@@ -2973,24 +2022,15 @@
         </is>
       </c>
       <c r="B106">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>1</v>
-      </c>
-      <c r="F106">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G106">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H106">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -3001,24 +2041,15 @@
         </is>
       </c>
       <c r="B107">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>1</v>
-      </c>
-      <c r="F107">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G107">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H107">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -3032,21 +2063,12 @@
         <v>1</v>
       </c>
       <c r="C108">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>1</v>
-      </c>
-      <c r="F108">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G108">
-        <v>0.029075361527879606</v>
-      </c>
-      <c r="H108">
         <v>0.0111614259199789</v>
       </c>
     </row>
@@ -3057,24 +2079,15 @@
         </is>
       </c>
       <c r="B109">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>1</v>
-      </c>
-      <c r="F109">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G109">
-        <v>5.710468118685689e-62</v>
-      </c>
-      <c r="H109">
         <v>2.681474812249094e-100</v>
       </c>
     </row>
@@ -3085,24 +2098,15 @@
         </is>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>1</v>
-      </c>
-      <c r="F110">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="G110">
-        <v>1.106832105034631e-45</v>
-      </c>
-      <c r="H110">
         <v>1.1149104355629062e-64</v>
       </c>
     </row>
